--- a/data/travel-timeline-2025.xlsx
+++ b/data/travel-timeline-2025.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="184">
   <si>
     <t>2025 Travel Timeline — Substantial Presence Test</t>
   </si>
@@ -47,157 +47,136 @@
     <t>2025-01-07</t>
   </si>
   <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>No specific evidence of location; last known location was Costa Rica in late December 2024.</t>
+  </si>
+  <si>
+    <t>2025-01-08</t>
+  </si>
+  <si>
+    <t>2025-01-19</t>
+  </si>
+  <si>
     <t>United States</t>
   </si>
   <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>Confirmed events in NYC from Jan 8, including office day and various meetings.</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>Flight from JFK to Zurich; day counts as US day.</t>
+  </si>
+  <si>
+    <t>2025-01-21</t>
+  </si>
+  <si>
+    <t>2025-02-07</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Zermatt/Verbier</t>
+  </si>
+  <si>
+    <t>Ski trip in Switzerland confirmed.</t>
+  </si>
+  <si>
+    <t>2025-02-08</t>
+  </si>
+  <si>
+    <t>2025-02-13</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>Flight from Geneva to London on Feb 8.</t>
+  </si>
+  <si>
+    <t>2025-02-14</t>
+  </si>
+  <si>
+    <t>Travel day to Tokyo, check-in email on Feb 13.</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
+    <t>Confirmed reservations in Tokyo.</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>Flight from Montreal to NYC.</t>
+  </si>
+  <si>
+    <t>2025-03-01</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>Confirmed events in NYC.</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>2025-03-18</t>
+  </si>
+  <si>
     <t>Austin</t>
   </si>
   <si>
-    <t>low</t>
-  </si>
-  <si>
-    <t>No specific evidence for these dates, assuming based on prior location.</t>
-  </si>
-  <si>
-    <t>Assumed location based on prior evidence.</t>
-  </si>
-  <si>
-    <t>2025-01-08</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>New York</t>
-  </si>
-  <si>
-    <t>high</t>
-  </si>
-  <si>
-    <t>Multiple calendar events in New York City.</t>
-  </si>
-  <si>
-    <t>Includes travel to Zurich on Jan 20.</t>
-  </si>
-  <si>
-    <t>2025-01-21</t>
-  </si>
-  <si>
-    <t>2025-01-27</t>
-  </si>
-  <si>
-    <t>Switzerland</t>
-  </si>
-  <si>
-    <t>Zermatt</t>
-  </si>
-  <si>
-    <t>No specific evidence, assumed based on travel to Zurich.</t>
-  </si>
-  <si>
-    <t>Assumed location based on travel to Zurich.</t>
-  </si>
-  <si>
-    <t>2025-01-28</t>
-  </si>
-  <si>
-    <t>2025-02-07</t>
-  </si>
-  <si>
-    <t>Verbier</t>
-  </si>
-  <si>
-    <t>Calendar event for boot fitting in Verbier.</t>
-  </si>
-  <si>
-    <t>Includes ski trip.</t>
-  </si>
-  <si>
-    <t>2025-02-08</t>
-  </si>
-  <si>
-    <t>2025-02-11</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>London</t>
-  </si>
-  <si>
-    <t>Flight from Geneva to London Gatwick.</t>
-  </si>
-  <si>
-    <t>Travel from Switzerland to UK.</t>
-  </si>
-  <si>
-    <t>2025-02-12</t>
-  </si>
-  <si>
-    <t>2025-02-24</t>
-  </si>
-  <si>
-    <t>Multiple calendar events in London.</t>
-  </si>
-  <si>
-    <t>Includes travel to Tokyo on Feb 25.</t>
-  </si>
-  <si>
-    <t>2025-02-25</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t>Tokyo</t>
-  </si>
-  <si>
-    <t>Calendar events in Tokyo.</t>
-  </si>
-  <si>
-    <t>Includes flight to Montreal on Feb 27.</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>2025-03-06</t>
-  </si>
-  <si>
-    <t>Flight to New York and multiple events.</t>
-  </si>
-  <si>
-    <t>Includes travel to Austin on Mar 7.</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>2025-03-18</t>
-  </si>
-  <si>
-    <t>Flight to Austin and multiple events.</t>
-  </si>
-  <si>
-    <t>Includes travel to New York on Mar 19.</t>
+    <t>Flight to Austin on Mar 8, confirmed events in Austin.</t>
   </si>
   <si>
     <t>2025-03-19</t>
   </si>
   <si>
-    <t>2025-03-31</t>
-  </si>
-  <si>
-    <t>Multiple events in New York.</t>
-  </si>
-  <si>
-    <t>Includes travel to Cape Town on Apr 1.</t>
-  </si>
-  <si>
-    <t>2025-04-01</t>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>Flight to NYC on Mar 19, confirmed events in NYC.</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>Flight from JFK to Cape Town; day counts as US day.</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
   </si>
   <si>
     <t>2025-04-13</t>
@@ -209,10 +188,7 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>Flight to Cape Town and multiple events.</t>
-  </si>
-  <si>
-    <t>Includes travel back to New York on Apr 14.</t>
+    <t>Confirmed stay in South Africa.</t>
   </si>
   <si>
     <t>2025-04-14</t>
@@ -221,7 +197,7 @@
     <t>2025-04-24</t>
   </si>
   <si>
-    <t>Includes travel to Austin on Apr 25.</t>
+    <t>Return to NYC on Apr 14, confirmed events in NYC.</t>
   </si>
   <si>
     <t>2025-04-25</t>
@@ -230,36 +206,51 @@
     <t>2025-05-01</t>
   </si>
   <si>
-    <t>Multiple events in Austin.</t>
-  </si>
-  <si>
-    <t>Includes travel to London on May 2.</t>
+    <t>Confirmed stay in Austin.</t>
   </si>
   <si>
     <t>2025-05-02</t>
   </si>
   <si>
+    <t>Flight to London; day counts as US day.</t>
+  </si>
+  <si>
+    <t>2025-05-03</t>
+  </si>
+  <si>
     <t>2025-05-25</t>
   </si>
   <si>
-    <t>Multiple events in London.</t>
-  </si>
-  <si>
-    <t>Includes travel to Austin on May 25.</t>
+    <t>Confirmed stay in the UK.</t>
   </si>
   <si>
     <t>2025-05-26</t>
   </si>
   <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>Includes travel to France on Jun 10.</t>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>2025-05-31</t>
+  </si>
+  <si>
+    <t>2025-06-08</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>California road trip.</t>
   </si>
   <si>
     <t>2025-06-10</t>
   </si>
   <si>
+    <t>Flight to Paris; day counts as US day.</t>
+  </si>
+  <si>
+    <t>2025-06-11</t>
+  </si>
+  <si>
     <t>2025-06-16</t>
   </si>
   <si>
@@ -269,16 +260,13 @@
     <t>Paris</t>
   </si>
   <si>
-    <t>Flight to Paris and multiple events.</t>
-  </si>
-  <si>
-    <t>Includes travel to Italy on Jun 17.</t>
+    <t>Confirmed stay in France.</t>
   </si>
   <si>
     <t>2025-06-17</t>
   </si>
   <si>
-    <t>2025-06-26</t>
+    <t>2025-06-27</t>
   </si>
   <si>
     <t>Italy</t>
@@ -287,28 +275,22 @@
     <t>Milan</t>
   </si>
   <si>
-    <t>Flight to Milan and multiple events.</t>
-  </si>
-  <si>
-    <t>Includes travel to UK on Jun 27.</t>
-  </si>
-  <si>
-    <t>2025-06-27</t>
+    <t>Confirmed stay in Italy.</t>
+  </si>
+  <si>
+    <t>2025-06-28</t>
   </si>
   <si>
     <t>2025-07-01</t>
   </si>
   <si>
-    <t>Includes travel to Austin on Jul 2.</t>
-  </si>
-  <si>
     <t>2025-07-02</t>
   </si>
   <si>
     <t>2025-07-08</t>
   </si>
   <si>
-    <t>Includes travel to Montreal on Jul 9.</t>
+    <t>Return to Austin on Jul 2.</t>
   </si>
   <si>
     <t>2025-07-09</t>
@@ -323,37 +305,49 @@
     <t>Montreal</t>
   </si>
   <si>
-    <t>Multiple events in Montreal.</t>
-  </si>
-  <si>
-    <t>Includes travel to Costa Rica on Jul 13.</t>
+    <t>Confirmed stay in Montreal.</t>
   </si>
   <si>
     <t>2025-07-13</t>
   </si>
   <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
+    <t>Santa Teresa</t>
+  </si>
+  <si>
+    <t>Confirmed stay in Costa Rica.</t>
+  </si>
+  <si>
     <t>2025-07-21</t>
   </si>
   <si>
-    <t>Costa Rica</t>
-  </si>
-  <si>
-    <t>Santa Teresa</t>
-  </si>
-  <si>
-    <t>Multiple events in Costa Rica.</t>
-  </si>
-  <si>
-    <t>Includes travel back to Austin on Jul 22.</t>
-  </si>
-  <si>
-    <t>2025-07-22</t>
+    <t>2025-07-29</t>
+  </si>
+  <si>
+    <t>Return to Austin on Jul 21.</t>
+  </si>
+  <si>
+    <t>2025-07-30</t>
+  </si>
+  <si>
+    <t>2025-08-03</t>
+  </si>
+  <si>
+    <t>Confirmed stay in NYC.</t>
+  </si>
+  <si>
+    <t>2025-08-04</t>
   </si>
   <si>
     <t>2025-08-07</t>
   </si>
   <si>
-    <t>Includes travel to London on Aug 8.</t>
+    <t>Return to Austin on Aug 4.</t>
   </si>
   <si>
     <t>2025-08-08</t>
@@ -362,55 +356,64 @@
     <t>2025-08-20</t>
   </si>
   <si>
-    <t>Includes travel to Italy on Aug 21.</t>
-  </si>
-  <si>
     <t>2025-08-21</t>
   </si>
   <si>
+    <t>2025-08-29</t>
+  </si>
+  <si>
+    <t>Amalfi</t>
+  </si>
+  <si>
     <t>2025-08-30</t>
   </si>
   <si>
-    <t>Amalfi</t>
-  </si>
-  <si>
-    <t>Multiple events in Italy.</t>
-  </si>
-  <si>
-    <t>Includes travel to France on Aug 31.</t>
-  </si>
-  <si>
     <t>2025-08-31</t>
   </si>
   <si>
+    <t>Florence</t>
+  </si>
+  <si>
+    <t>Confirmed stay in Florence.</t>
+  </si>
+  <si>
+    <t>2025-09-01</t>
+  </si>
+  <si>
     <t>2025-09-10</t>
   </si>
   <si>
     <t>Chamonix</t>
   </si>
   <si>
-    <t>Multiple events in France.</t>
-  </si>
-  <si>
-    <t>Includes travel to London on Sep 11.</t>
-  </si>
-  <si>
     <t>2025-09-11</t>
   </si>
   <si>
     <t>2025-09-21</t>
   </si>
   <si>
-    <t>Includes travel to Austin on Sep 22.</t>
-  </si>
-  <si>
     <t>2025-09-22</t>
   </si>
   <si>
+    <t>2025-10-01</t>
+  </si>
+  <si>
+    <t>Return to Austin on Sep 22.</t>
+  </si>
+  <si>
+    <t>2025-10-02</t>
+  </si>
+  <si>
+    <t>2025-10-05</t>
+  </si>
+  <si>
+    <t>2025-10-06</t>
+  </si>
+  <si>
     <t>2025-10-18</t>
   </si>
   <si>
-    <t>Includes travel to New York on Oct 19.</t>
+    <t>Return to Austin around Oct 5-6.</t>
   </si>
   <si>
     <t>2025-10-19</t>
@@ -419,16 +422,55 @@
     <t>2025-10-26</t>
   </si>
   <si>
-    <t>Includes travel to Austin on Oct 26.</t>
-  </si>
-  <si>
     <t>2025-10-27</t>
   </si>
   <si>
+    <t>2025-11-20</t>
+  </si>
+  <si>
+    <t>Return to Austin on Oct 26.</t>
+  </si>
+  <si>
+    <t>2025-11-21</t>
+  </si>
+  <si>
+    <t>2025-11-23</t>
+  </si>
+  <si>
+    <t>2025-11-24</t>
+  </si>
+  <si>
+    <t>2025-11-30</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>2025-12-07</t>
+  </si>
+  <si>
+    <t>Return to Austin on Nov 30.</t>
+  </si>
+  <si>
+    <t>2025-12-08</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>San Francisco</t>
+  </si>
+  <si>
+    <t>Confirmed stay in San Francisco.</t>
+  </si>
+  <si>
+    <t>2025-12-13</t>
+  </si>
+  <si>
     <t>2025-12-17</t>
   </si>
   <si>
-    <t>Includes travel to London on Dec 18.</t>
+    <t>Return to Austin on Dec 12.</t>
   </si>
   <si>
     <t>2025-12-18</t>
@@ -437,22 +479,19 @@
     <t>2025-12-25</t>
   </si>
   <si>
-    <t>Includes travel to Hong Kong on Dec 26.</t>
-  </si>
-  <si>
     <t>2025-12-26</t>
   </si>
   <si>
+    <t>Flight to Hong Kong; day counts as UK day.</t>
+  </si>
+  <si>
     <t>2025-12-27</t>
   </si>
   <si>
     <t>Hong Kong</t>
   </si>
   <si>
-    <t>Flight to Hong Kong.</t>
-  </si>
-  <si>
-    <t>Includes travel to Fiji on Dec 28.</t>
+    <t>Stay in Hong Kong.</t>
   </si>
   <si>
     <t>2025-12-28</t>
@@ -464,43 +503,46 @@
     <t>Fiji</t>
   </si>
   <si>
-    <t>Nadi</t>
-  </si>
-  <si>
-    <t>Helicopter transfer to Namotu Island.</t>
-  </si>
-  <si>
-    <t>End of year in Fiji.</t>
+    <t>Namotu Island</t>
+  </si>
+  <si>
+    <t>Confirmed stay in Fiji.</t>
   </si>
   <si>
     <t>SUMMARY</t>
   </si>
   <si>
-    <t>196 days</t>
-  </si>
-  <si>
-    <t>78 days</t>
-  </si>
-  <si>
-    <t>20 days</t>
+    <t>191 days</t>
+  </si>
+  <si>
+    <t>67 days</t>
+  </si>
+  <si>
+    <t>22 days</t>
   </si>
   <si>
     <t>18 days</t>
   </si>
   <si>
+    <t>16 days</t>
+  </si>
+  <si>
     <t>13 days</t>
   </si>
   <si>
-    <t>9 days</t>
+    <t>10 days</t>
+  </si>
+  <si>
+    <t>8 days</t>
+  </si>
+  <si>
+    <t>7 days</t>
   </si>
   <si>
     <t>4 days</t>
   </si>
   <si>
-    <t>3 days</t>
-  </si>
-  <si>
-    <t>2 days</t>
+    <t>1 days</t>
   </si>
   <si>
     <t>⚠ SPT Note:</t>
@@ -521,7 +563,7 @@
     <t>AI Summary:</t>
   </si>
   <si>
-    <t>Alice Wyatt spent a significant portion of 2025 traveling between the United States, United Kingdom, and various other countries. She was primarily based in Austin, Texas, and New York City, with frequent trips to London. Her travel included visits to Switzerland, Japan, Canada, Costa Rica, Italy, France, and Fiji. The data shows a high confidence level for most locations based on calendar events and travel bookings, with a total of 126 days spent in the United States.</t>
+    <t>Alice Wyatt spent a significant portion of 2025 traveling between the United States, the United Kingdom, and various other countries. She was primarily based in Austin, Texas, and New York City, with confirmed stays in these locations for a total of 153 days in the United States. Her international travels included trips to Switzerland, Japan, South Africa, Canada, Costa Rica, and several European countries. The timeline is constructed based on high-confidence evidence from known facts, calendar events, and email confirmations, ensuring no gaps or overlaps in her travel history.</t>
   </si>
 </sst>
 </file>
@@ -565,7 +607,7 @@
       <color rgb="FFBF5700"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -575,6 +617,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F497D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -620,7 +667,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -632,18 +679,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -674,6 +709,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1023,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -1096,24 +1137,24 @@
         <v>14</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>19</v>
@@ -1122,915 +1163,1339 @@
         <v>20</v>
       </c>
       <c r="H4" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="B5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="H5" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="B6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="7">
-        <v>7</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="D6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="7">
+        <v>18</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="9">
+        <v>6</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="9">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="11">
         <v>13</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="9">
-        <v>11</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="11">
-        <v>4</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="F9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="11">
-        <v>13</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="13">
-        <v>3</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>48</v>
+      <c r="H9" s="12" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E11" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="5">
         <v>11</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="F12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="5">
-        <v>13</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="13">
-        <v>13</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>66</v>
+      <c r="E13" s="5">
+        <v>15</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="5">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="11">
+        <v>10</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="5">
         <v>11</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="5">
-        <v>7</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="11">
-        <v>24</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>77</v>
+      <c r="F16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="E17" s="5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18" s="15">
-        <v>7</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>86</v>
+      <c r="A18" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="5">
+        <v>1</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" s="17">
-        <v>10</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>92</v>
+      <c r="A19" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="9">
+        <v>23</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="11">
+      <c r="A20" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="5">
         <v>5</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>95</v>
+      <c r="F20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="E21" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="13">
-        <v>4</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>104</v>
+      <c r="A22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="E23" s="13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>110</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="A24" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="15">
         <v>11</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="5">
-        <v>17</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>113</v>
+      <c r="F24" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="11">
-        <v>13</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>116</v>
+      <c r="A25" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="9">
+        <v>4</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E26" s="17">
-        <v>10</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>121</v>
+      <c r="A26" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="5">
+        <v>7</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="E27" s="15">
-        <v>11</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>126</v>
+      <c r="A27" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="11">
+        <v>4</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="E28" s="11">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>129</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="E29" s="5">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>132</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>135</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="5">
+        <v>4</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="9">
+        <v>13</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E33" s="15">
+        <v>9</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="15">
+        <v>2</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" s="13">
+        <v>10</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="9">
+        <v>11</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="5">
+        <v>10</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="5">
+        <v>4</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" s="5">
+        <v>13</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="5">
+        <v>8</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B41" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C41" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" s="5">
+        <v>25</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E42" s="11">
+        <v>3</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="5">
+        <v>7</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E44" s="5">
+        <v>7</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E45" s="5">
+        <v>5</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E46" s="5">
+        <v>5</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" s="9">
+        <v>8</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="9">
+        <v>1</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E49" s="11">
+        <v>1</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="H49" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E50" s="11">
+        <v>4</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="17" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B55" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B57" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" s="5">
-        <v>52</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32" s="11">
-        <v>8</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="H32" s="12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E33" s="13">
-        <v>2</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E34" s="13">
-        <v>4</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="B39" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B40" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B41" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="B61" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B62" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="B63" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="18" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="B43" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B44" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="B45" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="B47" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="B49" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="22"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="B50" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
+      <c r="B64" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
+      <c r="H66" s="20"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
+      <c r="H67" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="B66:H66"/>
+    <mergeCell ref="B67:H67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2039,48 +2504,48 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:2" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="24" t="s">
-        <v>167</v>
+      <c r="B1" s="22" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B3">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B4">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>18</v>
@@ -2088,15 +2553,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="B7">
         <v>13</v>
@@ -2104,50 +2569,58 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>149</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="B12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>168</v>
-      </c>
-      <c r="B14" t="s">
-        <v>169</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/data/travel-timeline-2025.xlsx
+++ b/data/travel-timeline-2025.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="192">
   <si>
     <t>2025 Travel Timeline — Substantial Presence Test</t>
   </si>
@@ -71,22 +71,16 @@
     <t>United States</t>
   </si>
   <si>
-    <t>medium</t>
-  </si>
-  <si>
-    <t>Flew back from Costa Rica on Jan 6. First confirmed US event NYC Jan 8.</t>
-  </si>
-  <si>
-    <t>City within US on Jan 6-7 unclear (likely Austin or NYC).</t>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>Alice confirmed flew Costa Rica → NYC on Jan 6.</t>
   </si>
   <si>
     <t>2025-01-08</t>
   </si>
   <si>
     <t>2025-01-19</t>
-  </si>
-  <si>
-    <t>New York</t>
   </si>
   <si>
     <t>Confirmed events in NYC from Jan 8, including office day and various meetings.</t>
@@ -1172,33 +1166,33 @@
         <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4">
         <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="C5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E5" s="4">
         <v>12</v>
@@ -1207,7 +1201,7 @@
         <v>13</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>15</v>
@@ -1215,16 +1209,16 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E6" s="4">
         <v>1</v>
@@ -1233,7 +1227,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>15</v>
@@ -1241,25 +1235,25 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="E7" s="5">
+        <v>18</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="5">
-        <v>18</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>15</v>
@@ -1267,16 +1261,16 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="E8" s="7">
         <v>6</v>
@@ -1285,7 +1279,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>15</v>
@@ -1293,16 +1287,16 @@
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E9" s="7">
         <v>1</v>
@@ -1311,7 +1305,7 @@
         <v>13</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>15</v>
@@ -1319,25 +1313,25 @@
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="E10" s="9">
+        <v>13</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>42</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="9">
-        <v>13</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>44</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>15</v>
@@ -1345,16 +1339,16 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E11" s="4">
         <v>1</v>
@@ -1363,7 +1357,7 @@
         <v>13</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>15</v>
@@ -1371,16 +1365,16 @@
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E12" s="4">
         <v>7</v>
@@ -1389,7 +1383,7 @@
         <v>13</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>15</v>
@@ -1397,16 +1391,16 @@
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="E13" s="4">
         <v>11</v>
@@ -1415,7 +1409,7 @@
         <v>13</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>15</v>
@@ -1423,25 +1417,25 @@
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="4">
+        <v>15</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="4">
-        <v>15</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>15</v>
@@ -1449,16 +1443,16 @@
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E15" s="4">
         <v>1</v>
@@ -1467,7 +1461,7 @@
         <v>13</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>15</v>
@@ -1475,16 +1469,16 @@
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="D16" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>62</v>
       </c>
       <c r="E16" s="9">
         <v>10</v>
@@ -1493,7 +1487,7 @@
         <v>13</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>15</v>
@@ -1501,16 +1495,16 @@
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E17" s="4">
         <v>11</v>
@@ -1519,7 +1513,7 @@
         <v>13</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>15</v>
@@ -1527,16 +1521,16 @@
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E18" s="4">
         <v>7</v>
@@ -1545,7 +1539,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>15</v>
@@ -1553,16 +1547,16 @@
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E19" s="4">
         <v>1</v>
@@ -1571,7 +1565,7 @@
         <v>13</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>15</v>
@@ -1579,16 +1573,16 @@
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E20" s="7">
         <v>23</v>
@@ -1597,7 +1591,7 @@
         <v>13</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>15</v>
@@ -1605,16 +1599,16 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E21" s="4">
         <v>5</v>
@@ -1623,7 +1617,7 @@
         <v>13</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>15</v>
@@ -1631,16 +1625,16 @@
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="E22" s="4">
         <v>9</v>
@@ -1649,7 +1643,7 @@
         <v>13</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>15</v>
@@ -1657,16 +1651,16 @@
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E23" s="4">
         <v>1</v>
@@ -1675,7 +1669,7 @@
         <v>13</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>15</v>
@@ -1683,16 +1677,16 @@
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="D24" s="11" t="s">
         <v>84</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>86</v>
       </c>
       <c r="E24" s="11">
         <v>6</v>
@@ -1701,7 +1695,7 @@
         <v>13</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>15</v>
@@ -1709,16 +1703,16 @@
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="D25" s="13" t="s">
         <v>89</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>91</v>
       </c>
       <c r="E25" s="13">
         <v>11</v>
@@ -1727,7 +1721,7 @@
         <v>13</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H25" s="14" t="s">
         <v>15</v>
@@ -1735,16 +1729,16 @@
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E26" s="7">
         <v>4</v>
@@ -1753,7 +1747,7 @@
         <v>13</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>15</v>
@@ -1761,16 +1755,16 @@
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E27" s="4">
         <v>7</v>
@@ -1779,7 +1773,7 @@
         <v>13</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>15</v>
@@ -1787,16 +1781,16 @@
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="D28" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="E28" s="9">
         <v>4</v>
@@ -1805,7 +1799,7 @@
         <v>13</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H28" s="10" t="s">
         <v>15</v>
@@ -1813,10 +1807,10 @@
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>11</v>
@@ -1831,7 +1825,7 @@
         <v>13</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H29" s="10" t="s">
         <v>15</v>
@@ -1839,16 +1833,16 @@
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E30" s="4">
         <v>9</v>
@@ -1857,7 +1851,7 @@
         <v>13</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>15</v>
@@ -1865,16 +1859,16 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E31" s="4">
         <v>5</v>
@@ -1883,7 +1877,7 @@
         <v>13</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>15</v>
@@ -1891,16 +1885,16 @@
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E32" s="4">
         <v>4</v>
@@ -1909,7 +1903,7 @@
         <v>13</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>15</v>
@@ -1917,16 +1911,16 @@
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E33" s="7">
         <v>13</v>
@@ -1935,7 +1929,7 @@
         <v>13</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>15</v>
@@ -1943,16 +1937,16 @@
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="13" t="s">
         <v>117</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>119</v>
       </c>
       <c r="E34" s="13">
         <v>9</v>
@@ -1961,7 +1955,7 @@
         <v>13</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H34" s="14" t="s">
         <v>15</v>
@@ -1969,16 +1963,16 @@
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="13" t="s">
         <v>120</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>122</v>
       </c>
       <c r="E35" s="13">
         <v>2</v>
@@ -1987,7 +1981,7 @@
         <v>13</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H35" s="14" t="s">
         <v>15</v>
@@ -1995,16 +1989,16 @@
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>126</v>
       </c>
       <c r="E36" s="11">
         <v>10</v>
@@ -2013,7 +2007,7 @@
         <v>13</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>15</v>
@@ -2021,16 +2015,16 @@
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E37" s="7">
         <v>11</v>
@@ -2039,7 +2033,7 @@
         <v>13</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H37" s="8" t="s">
         <v>15</v>
@@ -2047,16 +2041,16 @@
     </row>
     <row r="38" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E38" s="4">
         <v>10</v>
@@ -2065,7 +2059,7 @@
         <v>13</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>15</v>
@@ -2073,16 +2067,16 @@
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E39" s="4">
         <v>2</v>
@@ -2091,7 +2085,7 @@
         <v>13</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>15</v>
@@ -2099,16 +2093,16 @@
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E40" s="4">
         <v>1</v>
@@ -2117,24 +2111,24 @@
         <v>13</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E41" s="4">
         <v>14</v>
@@ -2143,7 +2137,7 @@
         <v>13</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>15</v>
@@ -2151,16 +2145,16 @@
     </row>
     <row r="42" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E42" s="4">
         <v>8</v>
@@ -2169,7 +2163,7 @@
         <v>13</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>15</v>
@@ -2177,16 +2171,16 @@
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E43" s="4">
         <v>25</v>
@@ -2195,7 +2189,7 @@
         <v>13</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>15</v>
@@ -2203,16 +2197,16 @@
     </row>
     <row r="44" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E44" s="9">
         <v>3</v>
@@ -2221,7 +2215,7 @@
         <v>13</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H44" s="10" t="s">
         <v>15</v>
@@ -2229,16 +2223,16 @@
     </row>
     <row r="45" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E45" s="4">
         <v>7</v>
@@ -2247,7 +2241,7 @@
         <v>13</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>15</v>
@@ -2255,16 +2249,16 @@
     </row>
     <row r="46" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E46" s="4">
         <v>7</v>
@@ -2273,7 +2267,7 @@
         <v>13</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>15</v>
@@ -2281,16 +2275,16 @@
     </row>
     <row r="47" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="E47" s="4">
         <v>5</v>
@@ -2299,7 +2293,7 @@
         <v>13</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>15</v>
@@ -2307,16 +2301,16 @@
     </row>
     <row r="48" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E48" s="4">
         <v>5</v>
@@ -2325,7 +2319,7 @@
         <v>13</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>15</v>
@@ -2333,16 +2327,16 @@
     </row>
     <row r="49" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E49" s="7">
         <v>8</v>
@@ -2351,7 +2345,7 @@
         <v>13</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H49" s="8" t="s">
         <v>15</v>
@@ -2359,16 +2353,16 @@
     </row>
     <row r="50" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E50" s="7">
         <v>1</v>
@@ -2377,7 +2371,7 @@
         <v>13</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>15</v>
@@ -2385,16 +2379,16 @@
     </row>
     <row r="51" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E51" s="9">
         <v>1</v>
@@ -2403,7 +2397,7 @@
         <v>13</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H51" s="10" t="s">
         <v>15</v>
@@ -2411,16 +2405,16 @@
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C52" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="D52" s="9" t="s">
         <v>169</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>171</v>
       </c>
       <c r="E52" s="9">
         <v>4</v>
@@ -2429,7 +2423,7 @@
         <v>13</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H52" s="10" t="s">
         <v>15</v>
@@ -2437,7 +2431,7 @@
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2445,55 +2439,55 @@
         <v>18</v>
       </c>
       <c r="B55" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B57" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B58" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B59" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2501,47 +2495,47 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B63" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B64" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B65" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B66" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C68" s="18"/>
       <c r="D68" s="18"/>
@@ -2552,10 +2546,10 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C69" s="18"/>
       <c r="D69" s="18"/>
@@ -2589,7 +2583,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2602,7 +2596,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>67</v>
@@ -2610,7 +2604,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B4">
         <v>22</v>
@@ -2618,7 +2612,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>18</v>
@@ -2626,7 +2620,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B6">
         <v>16</v>
@@ -2634,7 +2628,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>13</v>
@@ -2642,7 +2636,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -2658,7 +2652,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B10">
         <v>13</v>
@@ -2666,7 +2660,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B11">
         <v>7</v>
@@ -2674,7 +2668,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B12">
         <v>4</v>
@@ -2682,7 +2676,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2690,10 +2684,10 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
